--- a/output/pdf_financials_xlsx/PLUR.xlsx
+++ b/output/pdf_financials_xlsx/PLUR.xlsx
@@ -3541,19 +3541,19 @@
         <v>0</v>
       </c>
       <c r="C91" s="3" t="n">
-        <v>0</v>
+        <v>-0.008406</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0</v>
+        <v>-0.019092</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>0</v>
+        <v>-0.09317400000000001</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0</v>
+        <v>0.128806</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0</v>
+        <v>-0.09199499999999999</v>
       </c>
       <c r="H91" s="3" t="n">
         <v>0</v>
@@ -3574,7 +3574,7 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.116335</v>
       </c>
       <c r="D92" s="3" t="n">
         <v>0</v>
@@ -9092,7 +9092,11 @@
           <t>Foreign currency translation (deficit) reserve</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
@@ -10274,7 +10278,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>-</t>
@@ -11644,7 +11652,11 @@
           <t>Reserves (note 5)</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/PLUR.xlsx
+++ b/output/pdf_financials_xlsx/PLUR.xlsx
@@ -1617,7 +1617,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.27259</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.147433</v>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.27259</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.147433</v>
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.29259</v>
+        <v>0.02</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0.215905</v>
@@ -4712,16 +4712,16 @@
         <v>0</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.016775</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.0183</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>-0.0183</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>0</v>
+        <v>-0.042308</v>
       </c>
       <c r="G124" s="1" t="inlineStr">
         <is>
@@ -4749,16 +4749,16 @@
         <v>0</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.016775</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.0183</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>-0.0183</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0</v>
+        <v>-0.042308</v>
       </c>
       <c r="G125" s="1" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E109" s="5" t="n">
@@ -13646,7 +13646,11 @@
           <t>Lease payments 12</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
           <t>-</t>
@@ -15426,7 +15430,11 @@
           <t>Lease payments 9</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr"/>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E182" t="inlineStr">
         <is>
           <t>-</t>
@@ -18536,7 +18544,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
